--- a/supabase/datalama/excel/employee.xlsx
+++ b/supabase/datalama/excel/employee.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="424">
   <si>
     <t>id</t>
   </si>
@@ -1271,6 +1271,18 @@
   </si>
   <si>
     <t>Sumur Pecung</t>
+  </si>
+  <si>
+    <t>0f2462dbc16d4f7992d8e7ae63705f16</t>
+  </si>
+  <si>
+    <t>2026-05-02T13:28:44.058+00:00</t>
+  </si>
+  <si>
+    <t>bmbogor</t>
+  </si>
+  <si>
+    <t>bmbogor@email.com</t>
   </si>
 </sst>
 </file>
@@ -1657,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T50"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -4706,6 +4718,68 @@
         <v>31</v>
       </c>
     </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>420</v>
+      </c>
+      <c r="B51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" t="s">
+        <v>421</v>
+      </c>
+      <c r="D51" t="s">
+        <v>421</v>
+      </c>
+      <c r="E51" t="s">
+        <v>30</v>
+      </c>
+      <c r="F51" t="s">
+        <v>24</v>
+      </c>
+      <c r="G51" t="s">
+        <v>422</v>
+      </c>
+      <c r="H51" t="s">
+        <v>86</v>
+      </c>
+      <c r="I51" t="s">
+        <v>27</v>
+      </c>
+      <c r="J51" t="s">
+        <v>28</v>
+      </c>
+      <c r="K51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L51" t="s">
+        <v>30</v>
+      </c>
+      <c r="M51" t="s">
+        <v>423</v>
+      </c>
+      <c r="N51" t="s">
+        <v>144</v>
+      </c>
+      <c r="O51" t="s">
+        <v>180</v>
+      </c>
+      <c r="P51" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>186</v>
+      </c>
+      <c r="R51" t="s">
+        <v>187</v>
+      </c>
+      <c r="S51" t="s">
+        <v>49</v>
+      </c>
+      <c r="T51" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
